--- a/dataAcquisition/Motec_MP/channels/channels_ECUData.xlsx
+++ b/dataAcquisition/Motec_MP/channels/channels_ECUData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SimEnv\dataAcquisition\Motec_MP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SimEnv\dataAcquisition\Motec_MP\channels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DB1BE0-5566-4B3F-9D5B-B8636D34F751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296AA109-467C-491E-822F-77865C1E6583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{23B7CB8D-429B-4D61-8C73-6C5265DEBA20}"/>
+    <workbookView xWindow="57105" yWindow="-2625" windowWidth="17280" windowHeight="9960" xr2:uid="{23B7CB8D-429B-4D61-8C73-6C5265DEBA20}"/>
   </bookViews>
   <sheets>
     <sheet name="channels" sheetId="2" r:id="rId1"/>
@@ -1451,7 +1451,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA4F88A-3EEB-45AF-91DF-E65A060D6362}">
-  <dimension ref="A1:E991"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:E393"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.44140625" bestFit="1" customWidth="1"/>
@@ -4392,7 +4393,7 @@
         <v>334</v>
       </c>
       <c r="B366">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
@@ -4507,3065 +4508,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B381">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B382">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B383">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B384">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="385" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B385">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B386">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B387">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B388">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B389">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B390">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B391">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B392">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="393" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B393">
-        <v>1</v>
-      </c>
+    <row r="393" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C393">
         <v>5</v>
       </c>
       <c r="D393">
         <v>10</v>
-      </c>
-    </row>
-    <row r="394" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B394">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="395" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B395">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="396" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B396">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="397" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B397">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="398" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B398">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="399" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B399">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="400" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B400">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="401" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B401">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="402" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B402">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="403" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B403">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="404" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B404">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="405" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B405">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="406" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B406">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="407" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B407">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="408" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B408">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="409" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B409">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B410">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="411" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B411">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="412" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B412">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="413" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B413">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="414" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B414">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="415" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B415">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="416" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B416">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="417" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B417">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="418" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B418">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="419" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B419">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="420" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B420">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="421" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B421">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="422" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B422">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="423" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B423">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="424" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B424">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="425" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B425">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="426" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B426">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="427" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B427">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="428" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B428">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="429" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B429">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="430" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B430">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="431" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B431">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="432" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B432">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="433" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B433">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="434" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B434">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="435" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B435">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B436">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="437" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B437">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="438" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B438">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="439" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B439">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="440" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B440">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="441" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B441">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="442" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B442">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="443" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B443">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="444" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B444">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="445" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B445">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="446" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B446">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="447" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B447">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="448" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B448">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="449" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B449">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="450" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B450">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="451" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B451">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="452" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B452">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="453" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B453">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="454" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B454">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="455" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B455">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="456" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B456">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="457" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B457">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="458" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B458">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="459" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B459">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="460" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B460">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="461" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B461">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="462" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B462">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="463" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B463">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="464" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B464">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="465" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B465">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="466" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B466">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="467" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B467">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="468" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B468">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B469">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="470" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B470">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="471" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B471">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="472" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B472">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="473" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B473">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="474" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B474">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="475" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B475">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="476" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B476">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="477" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B477">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="478" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B478">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="479" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B479">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="480" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B480">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="481" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B481">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="482" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B482">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="483" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B483">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="484" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B484">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="485" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B485">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="486" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B486">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="487" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B487">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="488" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B488">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="489" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B489">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="490" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B490">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="491" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B491">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="492" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B492">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="493" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B493">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="494" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B494">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="495" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B495">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="496" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B496">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="497" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B497">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="498" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B498">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="499" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B499">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="500" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B500">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="501" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B501">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="502" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B502">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="503" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B503">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="504" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B504">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="505" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B505">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="506" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B506">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="507" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B507">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="508" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B508">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="509" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B509">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="510" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B510">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="511" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B511">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="512" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B512">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="513" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B513">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="514" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B514">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="515" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B515">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="516" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B516">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="517" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B517">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="518" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B518">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="519" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B519">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="520" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B520">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="521" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B521">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="522" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B522">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="523" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B523">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="524" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B524">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="525" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B525">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="526" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B526">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="527" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B527">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="528" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B528">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="529" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B529">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="530" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B530">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="531" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B531">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="532" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B532">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="533" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B533">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="534" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B534">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="535" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B535">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="536" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B536">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="537" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B537">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="538" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B538">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="539" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B539">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="540" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B540">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="541" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B541">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="542" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B542">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="543" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B543">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="544" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B544">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="545" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B545">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="546" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B546">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="547" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B547">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="548" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B548">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="549" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B549">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="550" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B550">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="551" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B551">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="552" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B552">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="553" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B553">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="554" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B554">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="555" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B555">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="556" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B556">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="557" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B557">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="558" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B558">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="559" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B559">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="560" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B560">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="561" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B561">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="562" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B562">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="563" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B563">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="564" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B564">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="565" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B565">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="566" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B566">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="567" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B567">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="568" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B568">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="569" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B569">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="570" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B570">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="571" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B571">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="572" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B572">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="573" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B573">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="574" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B574">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="575" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B575">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="576" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B576">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="577" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B577">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="578" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B578">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="579" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B579">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="580" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B580">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="581" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B581">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="582" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B582">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="583" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B583">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="584" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B584">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="585" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B585">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="586" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B586">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="587" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B587">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="588" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B588">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="589" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B589">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="590" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B590">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="591" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B591">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="592" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B592">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="593" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B593">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="594" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B594">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="595" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B595">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="596" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B596">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="597" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B597">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="598" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B598">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="599" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B599">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="600" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B600">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="601" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B601">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="602" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B602">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="603" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B603">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="604" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B604">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="605" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B605">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="606" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B606">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="607" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B607">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="608" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B608">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="609" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B609">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="610" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B610">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="611" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B611">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="612" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B612">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="613" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B613">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="614" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B614">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="615" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B615">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="616" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B616">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="617" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B617">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="618" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B618">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="619" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B619">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="620" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B620">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="621" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B621">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="622" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B622">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="623" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B623">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="624" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B624">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="625" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B625">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="626" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B626">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="627" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B627">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="628" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B628">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="629" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B629">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="630" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B630">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="631" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B631">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="632" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B632">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="633" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B633">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="634" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B634">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="635" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B635">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="636" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B636">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="637" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B637">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="638" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B638">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="639" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B639">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="640" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B640">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="641" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B641">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="642" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B642">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="643" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B643">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="644" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B644">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="645" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B645">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="646" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B646">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="647" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B647">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="648" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B648">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="649" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B649">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="650" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B650">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="651" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B651">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="652" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B652">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="653" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B653">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="654" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B654">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="655" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B655">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="656" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B656">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="657" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B657">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="658" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B658">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="659" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B659">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="660" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B660">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="661" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B661">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="662" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B662">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="663" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B663">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="664" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B664">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="665" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B665">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="666" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B666">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="667" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B667">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="668" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B668">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="669" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B669">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="670" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B670">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="671" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B671">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="672" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B672">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="673" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B673">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="674" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B674">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="675" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B675">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="676" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B676">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="677" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B677">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="678" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B678">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="679" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B679">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="680" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B680">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="681" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B681">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="682" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B682">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="683" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B683">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="684" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B684">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="685" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B685">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="686" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B686">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="687" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B687">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="688" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B688">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="689" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B689">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="690" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B690">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="691" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B691">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="692" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B692">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="693" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B693">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="694" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B694">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="695" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B695">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="696" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B696">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="697" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B697">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="698" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B698">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="699" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B699">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="700" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B700">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="701" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B701">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="702" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B702">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="703" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B703">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="704" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B704">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="705" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B705">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="706" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B706">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="707" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B707">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="708" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B708">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="709" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B709">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="710" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B710">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="711" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B711">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="712" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B712">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="713" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B713">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="714" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B714">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="715" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B715">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="716" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B716">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="717" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B717">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="718" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B718">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="719" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B719">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="720" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B720">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="721" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B721">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="722" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B722">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="723" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B723">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="724" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B724">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="725" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B725">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="726" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B726">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="727" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B727">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="728" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B728">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="729" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B729">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="730" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B730">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="731" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B731">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="732" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B732">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="733" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B733">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="734" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B734">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="735" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B735">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="736" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B736">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="737" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B737">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="738" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B738">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="739" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B739">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="740" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B740">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="741" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B741">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="742" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B742">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="743" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B743">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="744" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B744">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="745" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B745">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="746" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B746">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="747" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B747">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="748" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B748">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="749" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B749">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="750" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B750">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="751" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B751">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="752" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B752">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="753" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B753">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="754" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B754">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="755" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B755">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="756" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B756">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="757" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B757">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="758" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B758">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="759" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B759">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="760" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B760">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="761" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B761">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="762" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B762">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="763" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B763">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="764" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B764">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="765" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B765">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="766" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B766">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="767" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B767">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="768" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B768">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="769" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B769">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="770" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B770">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="771" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B771">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="772" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B772">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="773" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B773">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="774" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B774">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="775" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B775">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="776" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B776">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="777" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B777">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="778" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B778">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="779" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B779">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="780" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B780">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="781" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B781">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="782" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B782">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="783" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B783">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="784" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B784">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="785" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B785">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="786" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B786">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="787" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B787">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="788" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B788">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="789" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B789">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="790" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B790">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="791" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B791">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="792" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B792">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="793" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B793">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="794" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B794">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="795" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B795">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="796" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B796">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="797" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B797">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="798" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B798">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="799" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B799">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="800" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B800">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="801" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B801">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="802" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B802">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="803" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B803">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="804" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B804">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="805" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B805">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="806" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B806">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="807" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B807">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="808" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B808">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="809" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B809">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="810" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B810">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="811" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B811">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="812" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B812">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="813" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B813">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="814" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B814">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="815" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B815">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="816" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B816">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="817" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B817">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="818" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B818">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="819" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B819">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="820" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B820">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="821" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B821">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="822" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B822">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="823" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B823">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="824" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B824">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="825" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B825">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="826" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B826">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="827" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B827">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="828" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B828">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="829" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B829">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="830" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B830">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="831" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B831">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="832" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B832">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="833" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B833">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="834" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B834">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="835" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B835">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="836" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B836">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="837" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B837">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="838" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B838">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="839" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B839">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="840" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B840">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="841" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B841">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="842" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B842">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="843" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B843">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="844" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B844">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="845" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B845">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="846" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B846">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="847" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B847">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="848" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B848">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="849" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B849">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="850" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B850">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="851" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B851">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="852" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B852">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="853" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B853">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="854" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B854">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="855" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B855">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="856" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B856">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="857" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B857">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="858" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B858">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="859" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B859">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="860" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B860">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="861" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B861">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="862" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B862">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="863" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B863">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="864" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B864">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="865" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B865">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="866" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B866">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="867" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B867">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="868" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B868">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="869" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B869">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="870" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B870">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="871" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B871">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="872" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B872">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="873" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B873">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="874" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B874">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="875" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B875">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="876" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B876">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="877" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B877">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="878" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B878">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="879" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B879">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="880" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B880">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="881" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B881">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="882" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B882">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="883" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B883">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="884" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B884">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="885" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B885">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="886" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B886">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="887" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B887">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="888" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B888">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="889" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B889">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="890" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B890">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="891" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B891">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="892" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B892">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="893" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B893">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="894" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B894">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="895" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B895">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="896" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B896">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="897" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B897">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="898" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B898">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="899" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B899">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="900" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B900">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="901" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B901">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="902" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B902">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="903" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B903">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="904" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B904">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="905" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B905">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="906" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B906">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="907" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B907">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="908" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B908">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="909" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B909">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="910" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B910">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="911" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B911">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="912" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B912">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="913" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B913">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="914" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B914">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="915" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B915">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="916" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B916">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="917" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B917">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="918" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B918">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="919" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B919">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="920" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B920">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="921" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B921">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="922" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B922">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="923" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B923">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="924" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B924">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="925" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B925">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="926" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B926">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="927" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B927">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="928" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B928">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="929" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B929">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="930" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B930">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="931" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B931">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="932" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B932">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="933" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B933">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="934" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B934">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="935" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B935">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="936" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B936">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="937" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B937">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="938" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B938">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="939" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B939">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="940" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B940">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="941" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B941">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="942" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B942">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="943" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B943">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="944" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B944">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="945" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B945">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="946" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B946">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="947" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B947">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="948" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B948">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="949" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B949">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="950" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B950">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="951" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B951">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="952" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B952">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="953" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B953">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="954" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B954">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="955" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B955">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="956" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B956">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="957" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B957">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="958" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B958">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="959" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B959">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="960" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B960">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="961" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B961">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="962" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B962">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="963" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B963">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="964" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B964">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="965" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B965">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="966" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B966">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="967" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B967">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="968" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B968">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="969" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B969">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="970" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B970">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="971" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B971">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="972" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B972">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="973" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B973">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="974" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B974">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="975" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B975">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="976" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B976">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="977" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B977">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="978" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B978">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="979" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B979">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="980" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B980">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="981" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B981">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="982" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B982">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="983" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B983">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="984" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B984">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="985" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B985">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="986" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B986">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="987" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B987">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="988" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B988">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="989" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B989">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="990" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B990">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="991" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B991">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
